--- a/VibeProject1/Assets/Table/Item/Equipment.xlsx
+++ b/VibeProject1/Assets/Table/Item/Equipment.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,6 +426,34 @@
       <c r="B1" t="inlineStr">
         <is>
           <t>IconPath</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>placeholder-equipment-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>placeholder-equipment-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>placeholder-equipment-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>placeholder-equipment-4</t>
         </is>
       </c>
     </row>
@@ -440,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,6 +483,54 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>placeholder-equipment-1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Placeholder 장비 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>placeholder-equipment-2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Placeholder 장비 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>placeholder-equipment-3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Placeholder 장비 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>placeholder-equipment-4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Placeholder 장비 4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/VibeProject1/Assets/Table/Item/Equipment.xlsx
+++ b/VibeProject1/Assets/Table/Item/Equipment.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ItemStrings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ItemDetail" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ItemStrings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,18 +415,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
           <t>Id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>IconPath</t>
         </is>
       </c>
     </row>
@@ -468,66 +464,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>ItemId</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t>Id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Ko</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>placeholder-equipment-1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Placeholder 장비 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>placeholder-equipment-2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Placeholder 장비 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>placeholder-equipment-3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Placeholder 장비 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>placeholder-equipment-4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Placeholder 장비 4</t>
         </is>
       </c>
     </row>
